--- a/AWQP Water Processing ID Key_2026.xlsx
+++ b/AWQP Water Processing ID Key_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c7d62234183fd3ba/Documents/GitHub/ALS-Data-Cleaning-Tool/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ajbrown/Documents/GitHub/ALS-Data-Cleaning-Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="13_ncr:1_{6DF5ED64-21D9-4D79-8EBE-A27115C47507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BBDF0FF-1E71-4DCC-AD1A-D63E0D65ABD0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D1CD6E-5380-7044-B6D7-61356E637358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{80777274-BFA3-44C9-A50F-B90CEE9B5D11}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="19420" windowHeight="17480" activeTab="1" xr2:uid="{80777274-BFA3-44C9-A50F-B90CEE9B5D11}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="193">
   <si>
     <t>CSU Agricultural Water Quality Program Water Sample ID Protocols</t>
   </si>
@@ -170,9 +170,6 @@
     <t>CT2</t>
   </si>
   <si>
-    <t>TSS*</t>
-  </si>
-  <si>
     <t>E</t>
   </si>
   <si>
@@ -248,16 +245,10 @@
     <t>SC</t>
   </si>
   <si>
-    <t>pH*</t>
-  </si>
-  <si>
     <t>No treatment</t>
   </si>
   <si>
     <t>*blank*</t>
-  </si>
-  <si>
-    <t>Electrical Conductivity*</t>
   </si>
   <si>
     <t>*AWQP Standard Test Suite</t>
@@ -1286,6 +1277,12 @@
   </si>
   <si>
     <t>Karey Vilele Ranch Inflow</t>
+  </si>
+  <si>
+    <t>TSS, EC, pH*</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
 </sst>
 </file>
@@ -1759,7 +1756,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1869,9 +1866,6 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1884,6 +1878,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1893,25 +1903,10 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2004,7 +1999,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29C4907F-3B76-443A-AE2C-2301E0A39AD8}" name="Table1" displayName="Table1" ref="A6:D23" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29C4907F-3B76-443A-AE2C-2301E0A39AD8}" name="Table1" displayName="Table1" ref="A6:D23" totalsRowShown="0" headerRowBorderDxfId="5" tableBorderDxfId="4">
   <autoFilter ref="A6:D23" xr:uid="{29C4907F-3B76-443A-AE2C-2301E0A39AD8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:D23">
     <sortCondition ref="B6:B23"/>
@@ -2317,39 +2312,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5150FAAD-75A4-4303-8388-1924B1E28A85}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="39" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2368,25 +2363,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1"/>
-    <col min="6" max="6" width="3.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" style="1"/>
+    <col min="1" max="1" width="39.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" style="1"/>
+    <col min="6" max="6" width="3.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
@@ -2410,7 +2405,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -2433,7 +2428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -2456,12 +2451,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>19</v>
@@ -2479,12 +2474,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>24</v>
@@ -2494,537 +2489,537 @@
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="29" t="s">
-        <v>25</v>
+        <v>191</v>
       </c>
       <c r="H7" s="29">
         <v>4</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H9" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H10" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="D11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H11" s="1">
         <v>9</v>
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H13" s="1">
         <v>11</v>
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H14" s="1">
         <v>12</v>
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="H15" s="56">
+        <v>13</v>
+      </c>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" s="29">
-        <v>13</v>
-      </c>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="H16" s="43">
+      <c r="G16" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="H16" s="57">
         <v>14</v>
       </c>
-      <c r="I16" s="47"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I16" s="46"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B19" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D22" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D23" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D24" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D26" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D27" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D28" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D20" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D21" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D22" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D23" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D24" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D26" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D27" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="E28" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D29" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D29" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D34" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="1" t="s">
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D35" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G35" s="43"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G36" s="43"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G37" s="43"/>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G38" s="43"/>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G39" s="43"/>
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G40" s="43"/>
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
         <v>71</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D34" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D35" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G35" s="44"/>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D36" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G36" s="44"/>
-      <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G37" s="44"/>
-      <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G38" s="44"/>
-      <c r="J38" s="1"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G39" s="44"/>
-      <c r="J39" s="1"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G40" s="44"/>
-      <c r="J40" s="1"/>
-    </row>
-    <row r="41" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="12" t="s">
-        <v>74</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>7</v>
       </c>
       <c r="J41" s="1"/>
     </row>
-    <row r="42" spans="1:10" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>7</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>7</v>
       </c>
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="D44" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:10" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="14" t="s">
         <v>78</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J43" s="1"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G44" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J44" s="1"/>
-    </row>
-    <row r="45" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
-        <v>81</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="16"/>
       <c r="D46" s="16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="17"/>
@@ -3032,63 +3027,63 @@
       <c r="H46" s="17"/>
       <c r="I46" s="18"/>
     </row>
-    <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="26" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B47" s="6"/>
       <c r="I47" s="19"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="20"/>
       <c r="B48" s="6"/>
       <c r="D48" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I48" s="19"/>
+    </row>
+    <row r="49" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" s="54"/>
+      <c r="D49" s="32" t="s">
         <v>84</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="I48" s="19"/>
-    </row>
-    <row r="49" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="B49" s="49"/>
-      <c r="D49" s="32" t="s">
-        <v>87</v>
       </c>
       <c r="E49" s="33"/>
       <c r="F49" s="32" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G49" s="33"/>
       <c r="I49" s="19"/>
     </row>
-    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="27"/>
       <c r="B50" s="28"/>
       <c r="D50" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F50" s="31" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G50" s="7"/>
       <c r="I50" s="19"/>
     </row>
-    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="21" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B51" s="22"/>
       <c r="C51" s="22"/>
       <c r="D51" s="34" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E51" s="23"/>
       <c r="F51" s="34" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G51" s="23"/>
       <c r="H51" s="23"/>
@@ -3112,276 +3107,276 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39704DF2-44DD-430E-8EA6-D6DD65CB6F9B}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B5" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="53" t="s">
+      <c r="B18" s="49" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
-        <v>179</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="54" t="s">
+      <c r="C18" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D6" s="54" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
-        <v>144</v>
-      </c>
-      <c r="B7" s="56" t="s">
-        <v>177</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="D7" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="55" t="s">
-        <v>145</v>
-      </c>
-      <c r="B8" s="56" t="s">
-        <v>177</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>168</v>
-      </c>
-      <c r="D8" s="57" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>172</v>
-      </c>
-      <c r="D9" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="55" t="s">
-        <v>147</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="55" t="s">
-        <v>148</v>
-      </c>
-      <c r="B11" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="C11" s="57" t="s">
-        <v>190</v>
-      </c>
-      <c r="D11" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
-        <v>140</v>
-      </c>
-      <c r="B12" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="55" t="s">
-        <v>141</v>
-      </c>
-      <c r="B13" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>176</v>
-      </c>
-      <c r="D13" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="B14" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="C14" s="57" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="55" t="s">
-        <v>150</v>
-      </c>
-      <c r="B15" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>174</v>
-      </c>
-      <c r="D15" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="B16" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="C16" s="57" t="s">
-        <v>166</v>
-      </c>
-      <c r="D16" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="55" t="s">
-        <v>138</v>
-      </c>
-      <c r="B17" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="C17" s="57" t="s">
-        <v>166</v>
-      </c>
-      <c r="D17" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="55" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>166</v>
-      </c>
-      <c r="D18" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="55" t="s">
-        <v>142</v>
-      </c>
-      <c r="B20" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20" s="57" t="s">
-        <v>166</v>
-      </c>
-      <c r="D20" s="57" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="55" t="s">
-        <v>151</v>
-      </c>
-      <c r="B21" s="56" t="s">
-        <v>169</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>170</v>
-      </c>
-      <c r="D21" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="58" t="s">
-        <v>152</v>
-      </c>
-      <c r="B22" s="56" t="s">
-        <v>169</v>
-      </c>
-      <c r="C22" s="57" t="s">
-        <v>173</v>
-      </c>
-      <c r="D22" s="57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="55" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" s="56" t="s">
-        <v>178</v>
-      </c>
-      <c r="C23" s="57" t="s">
-        <v>168</v>
-      </c>
-      <c r="D23" s="57" t="s">
-        <v>70</v>
+      <c r="D23" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3398,219 +3393,219 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730A1B85-7951-4488-BC37-3DB089A0E115}">
   <dimension ref="A1:P343"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="1"/>
-    <col min="3" max="3" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="1"/>
+    <col min="3" max="3" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="F1" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I1" s="36" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C2" s="37"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C3" s="37"/>
       <c r="F3" s="33"/>
-      <c r="I3" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I3" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="55"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C4" s="37"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C5" s="37"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C6" s="37"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="50"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="55"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="55"/>
+      <c r="P6" s="55"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="37"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="50"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="55"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="37"/>
       <c r="F8" s="33"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="50"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="55"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="37"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="50"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="55"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="37"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="50"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="55"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="55"/>
+      <c r="P10" s="55"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="37"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="37"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="37"/>
       <c r="F13" s="33"/>
       <c r="I13" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="37"/>
       <c r="I14" s="38" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="37"/>
       <c r="I15" s="38" t="b">
         <f>IF(ISNUMBER(SEARCH("-D",B36)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C16" s="37"/>
       <c r="I16" s="38" t="b">
         <f>IF(ISNUMBER(SEARCH("-D",B37)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C17" s="37"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C18" s="37"/>
       <c r="F18" s="33"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C19" s="37"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C20" s="37"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C21" s="37"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C22" s="37"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C23" s="37"/>
       <c r="F23" s="33"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C24" s="37"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C25" s="37"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C26" s="37"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C27" s="37"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C28" s="37"/>
       <c r="F28" s="33"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C29" s="37"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C30" s="37"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C31" s="37"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32"/>
       <c r="B32"/>
       <c r="C32"/>
@@ -3619,7 +3614,7 @@
       <c r="F32"/>
       <c r="G32"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33"/>
       <c r="B33"/>
       <c r="C33"/>
@@ -3628,7 +3623,7 @@
       <c r="F33"/>
       <c r="G33"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34"/>
       <c r="B34"/>
       <c r="C34"/>
@@ -3637,7 +3632,7 @@
       <c r="F34"/>
       <c r="G34"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35"/>
@@ -3646,7 +3641,7 @@
       <c r="F35"/>
       <c r="G35"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36"/>
       <c r="B36"/>
       <c r="C36"/>
@@ -3655,7 +3650,7 @@
       <c r="F36"/>
       <c r="G36"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37"/>
       <c r="B37"/>
       <c r="C37"/>
@@ -3664,7 +3659,7 @@
       <c r="F37"/>
       <c r="G37"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38"/>
       <c r="B38"/>
       <c r="C38"/>
@@ -3673,7 +3668,7 @@
       <c r="F38"/>
       <c r="G38"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39"/>
       <c r="B39"/>
       <c r="C39"/>
@@ -3682,7 +3677,7 @@
       <c r="F39"/>
       <c r="G39"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40"/>
       <c r="B40"/>
       <c r="C40"/>
@@ -3691,7 +3686,7 @@
       <c r="F40"/>
       <c r="G40"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41"/>
       <c r="B41"/>
       <c r="C41"/>
@@ -3700,7 +3695,7 @@
       <c r="F41"/>
       <c r="G41"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42"/>
@@ -3709,7 +3704,7 @@
       <c r="F42"/>
       <c r="G42"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
@@ -3718,7 +3713,7 @@
       <c r="F43"/>
       <c r="G43"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44"/>
       <c r="B44"/>
       <c r="C44"/>
@@ -3727,7 +3722,7 @@
       <c r="F44"/>
       <c r="G44"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45"/>
       <c r="B45"/>
       <c r="C45"/>
@@ -3736,7 +3731,7 @@
       <c r="F45"/>
       <c r="G45"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
@@ -3745,7 +3740,7 @@
       <c r="F46"/>
       <c r="G46"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47"/>
       <c r="B47"/>
       <c r="C47"/>
@@ -3754,7 +3749,7 @@
       <c r="F47"/>
       <c r="G47"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48"/>
       <c r="B48"/>
       <c r="C48"/>
@@ -3763,7 +3758,7 @@
       <c r="F48"/>
       <c r="G48"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49"/>
@@ -3772,7 +3767,7 @@
       <c r="F49"/>
       <c r="G49"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50"/>
       <c r="B50"/>
       <c r="C50"/>
@@ -3781,7 +3776,7 @@
       <c r="F50"/>
       <c r="G50"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51"/>
       <c r="B51"/>
       <c r="C51"/>
@@ -3790,7 +3785,7 @@
       <c r="F51"/>
       <c r="G51"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52"/>
       <c r="B52"/>
       <c r="C52"/>
@@ -3799,7 +3794,7 @@
       <c r="F52"/>
       <c r="G52"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53"/>
       <c r="B53"/>
       <c r="C53"/>
@@ -3808,7 +3803,7 @@
       <c r="F53"/>
       <c r="G53"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54"/>
       <c r="B54"/>
       <c r="C54"/>
@@ -3817,7 +3812,7 @@
       <c r="F54"/>
       <c r="G54"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55"/>
@@ -3826,7 +3821,7 @@
       <c r="F55"/>
       <c r="G55"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56"/>
       <c r="B56"/>
       <c r="C56"/>
@@ -3835,7 +3830,7 @@
       <c r="F56"/>
       <c r="G56"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57"/>
@@ -3844,7 +3839,7 @@
       <c r="F57"/>
       <c r="G57"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58"/>
@@ -3853,7 +3848,7 @@
       <c r="F58"/>
       <c r="G58"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59"/>
       <c r="B59"/>
       <c r="C59"/>
@@ -3862,7 +3857,7 @@
       <c r="F59"/>
       <c r="G59"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60"/>
       <c r="B60"/>
       <c r="C60"/>
@@ -3871,7 +3866,7 @@
       <c r="F60"/>
       <c r="G60"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61"/>
@@ -3880,7 +3875,7 @@
       <c r="F61"/>
       <c r="G61"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62"/>
       <c r="B62"/>
       <c r="C62"/>
@@ -3889,7 +3884,7 @@
       <c r="F62"/>
       <c r="G62"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63"/>
       <c r="B63"/>
       <c r="C63"/>
@@ -3898,7 +3893,7 @@
       <c r="F63"/>
       <c r="G63"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64"/>
       <c r="B64"/>
       <c r="C64"/>
@@ -3907,7 +3902,7 @@
       <c r="F64"/>
       <c r="G64"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65"/>
       <c r="B65"/>
       <c r="C65"/>
@@ -3916,7 +3911,7 @@
       <c r="F65"/>
       <c r="G65"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66"/>
       <c r="B66"/>
       <c r="C66"/>
@@ -3925,7 +3920,7 @@
       <c r="F66"/>
       <c r="G66"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67"/>
       <c r="B67"/>
       <c r="C67"/>
@@ -3934,7 +3929,7 @@
       <c r="F67"/>
       <c r="G67"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68"/>
       <c r="B68"/>
       <c r="C68"/>
@@ -3943,7 +3938,7 @@
       <c r="F68"/>
       <c r="G68"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69"/>
       <c r="B69"/>
       <c r="C69"/>
@@ -3952,7 +3947,7 @@
       <c r="F69"/>
       <c r="G69"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70"/>
       <c r="B70"/>
       <c r="C70"/>
@@ -3961,7 +3956,7 @@
       <c r="F70"/>
       <c r="G70"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71"/>
       <c r="B71"/>
       <c r="C71"/>
@@ -3970,7 +3965,7 @@
       <c r="F71"/>
       <c r="G71"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72"/>
       <c r="B72"/>
       <c r="C72"/>
@@ -3979,7 +3974,7 @@
       <c r="F72"/>
       <c r="G72"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73"/>
       <c r="B73"/>
       <c r="C73"/>
@@ -3988,7 +3983,7 @@
       <c r="F73"/>
       <c r="G73"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74"/>
       <c r="B74"/>
       <c r="C74"/>
@@ -3997,7 +3992,7 @@
       <c r="F74"/>
       <c r="G74"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75"/>
       <c r="B75"/>
       <c r="C75"/>
@@ -4006,7 +4001,7 @@
       <c r="F75"/>
       <c r="G75"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76"/>
       <c r="B76"/>
       <c r="C76"/>
@@ -4015,7 +4010,7 @@
       <c r="F76"/>
       <c r="G76"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77"/>
       <c r="B77"/>
       <c r="C77"/>
@@ -4024,7 +4019,7 @@
       <c r="F77"/>
       <c r="G77"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78"/>
       <c r="B78"/>
       <c r="C78"/>
@@ -4033,7 +4028,7 @@
       <c r="F78"/>
       <c r="G78"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79"/>
       <c r="B79"/>
       <c r="C79"/>
@@ -4042,7 +4037,7 @@
       <c r="F79"/>
       <c r="G79"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80"/>
       <c r="B80"/>
       <c r="C80"/>
@@ -4051,7 +4046,7 @@
       <c r="F80"/>
       <c r="G80"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81"/>
       <c r="B81"/>
       <c r="C81"/>
@@ -4060,7 +4055,7 @@
       <c r="F81"/>
       <c r="G81"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82"/>
       <c r="B82"/>
       <c r="C82"/>
@@ -4069,7 +4064,7 @@
       <c r="F82"/>
       <c r="G82"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83"/>
       <c r="B83"/>
       <c r="C83"/>
@@ -4078,7 +4073,7 @@
       <c r="F83"/>
       <c r="G83"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84"/>
       <c r="B84"/>
       <c r="C84"/>
@@ -4087,7 +4082,7 @@
       <c r="F84"/>
       <c r="G84"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85"/>
       <c r="B85"/>
       <c r="C85"/>
@@ -4096,7 +4091,7 @@
       <c r="F85"/>
       <c r="G85"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86"/>
       <c r="B86"/>
       <c r="C86"/>
@@ -4105,7 +4100,7 @@
       <c r="F86"/>
       <c r="G86"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87"/>
       <c r="B87"/>
       <c r="C87"/>
@@ -4114,7 +4109,7 @@
       <c r="F87"/>
       <c r="G87"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88"/>
       <c r="B88"/>
       <c r="C88"/>
@@ -4123,7 +4118,7 @@
       <c r="F88"/>
       <c r="G88"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89"/>
       <c r="B89"/>
       <c r="C89"/>
@@ -4132,7 +4127,7 @@
       <c r="F89"/>
       <c r="G89"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90"/>
       <c r="B90"/>
       <c r="C90"/>
@@ -4141,7 +4136,7 @@
       <c r="F90"/>
       <c r="G90"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91"/>
       <c r="B91"/>
       <c r="C91"/>
@@ -4150,7 +4145,7 @@
       <c r="F91"/>
       <c r="G91"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92"/>
       <c r="B92"/>
       <c r="C92"/>
@@ -4159,7 +4154,7 @@
       <c r="F92"/>
       <c r="G92"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93"/>
       <c r="B93"/>
       <c r="C93"/>
@@ -4168,7 +4163,7 @@
       <c r="F93"/>
       <c r="G93"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94"/>
       <c r="B94"/>
       <c r="C94"/>
@@ -4177,7 +4172,7 @@
       <c r="F94"/>
       <c r="G94"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95"/>
       <c r="B95"/>
       <c r="C95"/>
@@ -4186,7 +4181,7 @@
       <c r="F95"/>
       <c r="G95"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96"/>
       <c r="B96"/>
       <c r="C96"/>
@@ -4195,7 +4190,7 @@
       <c r="F96"/>
       <c r="G96"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97"/>
       <c r="B97"/>
       <c r="C97"/>
@@ -4204,7 +4199,7 @@
       <c r="F97"/>
       <c r="G97"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98"/>
       <c r="B98"/>
       <c r="C98"/>
@@ -4213,7 +4208,7 @@
       <c r="F98"/>
       <c r="G98"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99"/>
       <c r="B99"/>
       <c r="C99"/>
@@ -4222,7 +4217,7 @@
       <c r="F99"/>
       <c r="G99"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100"/>
       <c r="B100"/>
       <c r="C100"/>
@@ -4231,7 +4226,7 @@
       <c r="F100"/>
       <c r="G100"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101"/>
@@ -4240,7 +4235,7 @@
       <c r="F101"/>
       <c r="G101"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102"/>
       <c r="B102"/>
       <c r="C102"/>
@@ -4249,7 +4244,7 @@
       <c r="F102"/>
       <c r="G102"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103"/>
       <c r="B103"/>
       <c r="C103"/>
@@ -4258,7 +4253,7 @@
       <c r="F103"/>
       <c r="G103"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104"/>
       <c r="B104"/>
       <c r="C104"/>
@@ -4267,7 +4262,7 @@
       <c r="F104"/>
       <c r="G104"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105"/>
       <c r="B105"/>
       <c r="C105"/>
@@ -4276,7 +4271,7 @@
       <c r="F105"/>
       <c r="G105"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106"/>
       <c r="B106"/>
       <c r="C106"/>
@@ -4285,7 +4280,7 @@
       <c r="F106"/>
       <c r="G106"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107"/>
       <c r="B107"/>
       <c r="C107"/>
@@ -4294,7 +4289,7 @@
       <c r="F107"/>
       <c r="G107"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108"/>
       <c r="B108"/>
       <c r="C108"/>
@@ -4303,7 +4298,7 @@
       <c r="F108"/>
       <c r="G108"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109"/>
       <c r="B109"/>
       <c r="C109"/>
@@ -4312,7 +4307,7 @@
       <c r="F109"/>
       <c r="G109"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110"/>
       <c r="B110"/>
       <c r="C110"/>
@@ -4321,7 +4316,7 @@
       <c r="F110"/>
       <c r="G110"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111"/>
       <c r="B111"/>
       <c r="C111"/>
@@ -4330,7 +4325,7 @@
       <c r="F111"/>
       <c r="G111"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112"/>
       <c r="B112"/>
       <c r="C112"/>
@@ -4339,7 +4334,7 @@
       <c r="F112"/>
       <c r="G112"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113"/>
       <c r="B113"/>
       <c r="C113"/>
@@ -4348,7 +4343,7 @@
       <c r="F113"/>
       <c r="G113"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114"/>
       <c r="B114"/>
       <c r="C114"/>
@@ -4357,7 +4352,7 @@
       <c r="F114"/>
       <c r="G114"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115"/>
       <c r="B115"/>
       <c r="C115"/>
@@ -4366,7 +4361,7 @@
       <c r="F115"/>
       <c r="G115"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116"/>
       <c r="B116"/>
       <c r="C116"/>
@@ -4375,7 +4370,7 @@
       <c r="F116"/>
       <c r="G116"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117"/>
       <c r="B117"/>
       <c r="C117"/>
@@ -4384,7 +4379,7 @@
       <c r="F117"/>
       <c r="G117"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118"/>
       <c r="B118"/>
       <c r="C118"/>
@@ -4393,7 +4388,7 @@
       <c r="F118"/>
       <c r="G118"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119"/>
       <c r="B119"/>
       <c r="C119"/>
@@ -4402,7 +4397,7 @@
       <c r="F119"/>
       <c r="G119"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120"/>
       <c r="B120"/>
       <c r="C120"/>
@@ -4411,7 +4406,7 @@
       <c r="F120"/>
       <c r="G120"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121"/>
       <c r="B121"/>
       <c r="C121"/>
@@ -4420,7 +4415,7 @@
       <c r="F121"/>
       <c r="G121"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122"/>
       <c r="B122"/>
       <c r="C122"/>
@@ -4429,7 +4424,7 @@
       <c r="F122"/>
       <c r="G122"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123"/>
       <c r="B123"/>
       <c r="C123"/>
@@ -4438,7 +4433,7 @@
       <c r="F123"/>
       <c r="G123"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124"/>
       <c r="B124"/>
       <c r="C124"/>
@@ -4447,7 +4442,7 @@
       <c r="F124"/>
       <c r="G124"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125"/>
       <c r="B125"/>
       <c r="C125"/>
@@ -4456,7 +4451,7 @@
       <c r="F125"/>
       <c r="G125"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126"/>
       <c r="B126"/>
       <c r="C126"/>
@@ -4465,7 +4460,7 @@
       <c r="F126"/>
       <c r="G126"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127"/>
       <c r="B127"/>
       <c r="C127"/>
@@ -4474,7 +4469,7 @@
       <c r="F127"/>
       <c r="G127"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128"/>
       <c r="B128"/>
       <c r="C128"/>
@@ -4483,7 +4478,7 @@
       <c r="F128"/>
       <c r="G128"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129"/>
       <c r="B129"/>
       <c r="C129"/>
@@ -4492,7 +4487,7 @@
       <c r="F129"/>
       <c r="G129"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130"/>
       <c r="B130"/>
       <c r="C130"/>
@@ -4501,7 +4496,7 @@
       <c r="F130"/>
       <c r="G130"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131"/>
       <c r="B131"/>
       <c r="C131"/>
@@ -4510,7 +4505,7 @@
       <c r="F131"/>
       <c r="G131"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132"/>
       <c r="B132"/>
       <c r="C132"/>
@@ -4519,7 +4514,7 @@
       <c r="F132"/>
       <c r="G132"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133"/>
       <c r="B133"/>
       <c r="C133"/>
@@ -4528,7 +4523,7 @@
       <c r="F133"/>
       <c r="G133"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134"/>
       <c r="B134"/>
       <c r="C134"/>
@@ -4537,7 +4532,7 @@
       <c r="F134"/>
       <c r="G134"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135"/>
       <c r="B135"/>
       <c r="C135"/>
@@ -4546,7 +4541,7 @@
       <c r="F135"/>
       <c r="G135"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136"/>
       <c r="B136"/>
       <c r="C136"/>
@@ -4555,7 +4550,7 @@
       <c r="F136"/>
       <c r="G136"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137"/>
       <c r="B137"/>
       <c r="C137"/>
@@ -4564,7 +4559,7 @@
       <c r="F137"/>
       <c r="G137"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138"/>
       <c r="B138"/>
       <c r="C138"/>
@@ -4573,7 +4568,7 @@
       <c r="F138"/>
       <c r="G138"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139"/>
       <c r="B139"/>
       <c r="C139"/>
@@ -4582,7 +4577,7 @@
       <c r="F139"/>
       <c r="G139"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140"/>
       <c r="B140"/>
       <c r="C140"/>
@@ -4591,7 +4586,7 @@
       <c r="F140"/>
       <c r="G140"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141"/>
       <c r="B141"/>
       <c r="C141"/>
@@ -4600,7 +4595,7 @@
       <c r="F141"/>
       <c r="G141"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142"/>
       <c r="B142"/>
       <c r="C142"/>
@@ -4609,7 +4604,7 @@
       <c r="F142"/>
       <c r="G142"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143"/>
       <c r="B143"/>
       <c r="C143"/>
@@ -4618,7 +4613,7 @@
       <c r="F143"/>
       <c r="G143"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144"/>
       <c r="B144"/>
       <c r="C144"/>
@@ -4627,7 +4622,7 @@
       <c r="F144"/>
       <c r="G144"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145"/>
       <c r="B145"/>
       <c r="C145"/>
@@ -4636,7 +4631,7 @@
       <c r="F145"/>
       <c r="G145"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146"/>
       <c r="B146"/>
       <c r="C146"/>
@@ -4645,7 +4640,7 @@
       <c r="F146"/>
       <c r="G146"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147"/>
       <c r="B147"/>
       <c r="C147"/>
@@ -4654,7 +4649,7 @@
       <c r="F147"/>
       <c r="G147"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148"/>
       <c r="B148"/>
       <c r="C148"/>
@@ -4663,7 +4658,7 @@
       <c r="F148"/>
       <c r="G148"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149"/>
       <c r="B149"/>
       <c r="C149"/>
@@ -4672,7 +4667,7 @@
       <c r="F149"/>
       <c r="G149"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150"/>
       <c r="B150"/>
       <c r="C150"/>
@@ -4681,7 +4676,7 @@
       <c r="F150"/>
       <c r="G150"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151"/>
       <c r="B151"/>
       <c r="C151"/>
@@ -4690,7 +4685,7 @@
       <c r="F151"/>
       <c r="G151"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152"/>
       <c r="B152"/>
       <c r="C152"/>
@@ -4699,7 +4694,7 @@
       <c r="F152"/>
       <c r="G152"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153"/>
       <c r="B153"/>
       <c r="C153"/>
@@ -4708,7 +4703,7 @@
       <c r="F153"/>
       <c r="G153"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154"/>
       <c r="B154"/>
       <c r="C154"/>
@@ -4717,7 +4712,7 @@
       <c r="F154"/>
       <c r="G154"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155"/>
       <c r="B155"/>
       <c r="C155"/>
@@ -4726,7 +4721,7 @@
       <c r="F155"/>
       <c r="G155"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156"/>
       <c r="B156"/>
       <c r="C156"/>
@@ -4735,7 +4730,7 @@
       <c r="F156"/>
       <c r="G156"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157"/>
       <c r="B157"/>
       <c r="C157"/>
@@ -4744,7 +4739,7 @@
       <c r="F157"/>
       <c r="G157"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158"/>
       <c r="B158"/>
       <c r="C158"/>
@@ -4753,7 +4748,7 @@
       <c r="F158"/>
       <c r="G158"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159"/>
       <c r="B159"/>
       <c r="C159"/>
@@ -4762,7 +4757,7 @@
       <c r="F159"/>
       <c r="G159"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160"/>
       <c r="B160"/>
       <c r="C160"/>
@@ -4771,7 +4766,7 @@
       <c r="F160"/>
       <c r="G160"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161"/>
       <c r="B161"/>
       <c r="C161"/>
@@ -4780,7 +4775,7 @@
       <c r="F161"/>
       <c r="G161"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162"/>
       <c r="B162"/>
       <c r="C162"/>
@@ -4789,7 +4784,7 @@
       <c r="F162"/>
       <c r="G162"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163"/>
       <c r="B163"/>
       <c r="C163"/>
@@ -4798,7 +4793,7 @@
       <c r="F163"/>
       <c r="G163"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164"/>
       <c r="B164"/>
       <c r="C164"/>
@@ -4807,7 +4802,7 @@
       <c r="F164"/>
       <c r="G164"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165"/>
       <c r="B165"/>
       <c r="C165"/>
@@ -4816,7 +4811,7 @@
       <c r="F165"/>
       <c r="G165"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166"/>
       <c r="B166"/>
       <c r="C166"/>
@@ -4825,7 +4820,7 @@
       <c r="F166"/>
       <c r="G166"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167"/>
       <c r="B167"/>
       <c r="C167"/>
@@ -4834,7 +4829,7 @@
       <c r="F167"/>
       <c r="G167"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168"/>
       <c r="B168"/>
       <c r="C168"/>
@@ -4843,7 +4838,7 @@
       <c r="F168"/>
       <c r="G168"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169"/>
       <c r="B169"/>
       <c r="C169"/>
@@ -4852,7 +4847,7 @@
       <c r="F169"/>
       <c r="G169"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170"/>
       <c r="B170"/>
       <c r="C170"/>
@@ -4861,7 +4856,7 @@
       <c r="F170"/>
       <c r="G170"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171"/>
       <c r="B171"/>
       <c r="C171"/>
@@ -4870,7 +4865,7 @@
       <c r="F171"/>
       <c r="G171"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172"/>
       <c r="B172"/>
       <c r="C172"/>
@@ -4879,7 +4874,7 @@
       <c r="F172"/>
       <c r="G172"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173"/>
       <c r="B173"/>
       <c r="C173"/>
@@ -4888,7 +4883,7 @@
       <c r="F173"/>
       <c r="G173"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174"/>
       <c r="B174"/>
       <c r="C174"/>
@@ -4897,7 +4892,7 @@
       <c r="F174"/>
       <c r="G174"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175"/>
       <c r="B175"/>
       <c r="C175"/>
@@ -4906,7 +4901,7 @@
       <c r="F175"/>
       <c r="G175"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176"/>
       <c r="B176"/>
       <c r="C176"/>
@@ -4915,7 +4910,7 @@
       <c r="F176"/>
       <c r="G176"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177"/>
       <c r="B177"/>
       <c r="C177"/>
@@ -4924,7 +4919,7 @@
       <c r="F177"/>
       <c r="G177"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178"/>
       <c r="B178"/>
       <c r="C178"/>
@@ -4933,7 +4928,7 @@
       <c r="F178"/>
       <c r="G178"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179"/>
       <c r="B179"/>
       <c r="C179"/>
@@ -4942,7 +4937,7 @@
       <c r="F179"/>
       <c r="G179"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180"/>
       <c r="B180"/>
       <c r="C180"/>
@@ -4951,7 +4946,7 @@
       <c r="F180"/>
       <c r="G180"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181"/>
       <c r="B181"/>
       <c r="C181"/>
@@ -4960,7 +4955,7 @@
       <c r="F181"/>
       <c r="G181"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182"/>
       <c r="B182"/>
       <c r="C182"/>
@@ -4969,7 +4964,7 @@
       <c r="F182"/>
       <c r="G182"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183"/>
       <c r="B183"/>
       <c r="C183"/>
@@ -4978,7 +4973,7 @@
       <c r="F183"/>
       <c r="G183"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184"/>
       <c r="B184"/>
       <c r="C184"/>
@@ -4987,7 +4982,7 @@
       <c r="F184"/>
       <c r="G184"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185"/>
       <c r="B185"/>
       <c r="C185"/>
@@ -4996,7 +4991,7 @@
       <c r="F185"/>
       <c r="G185"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186"/>
       <c r="B186"/>
       <c r="C186"/>
@@ -5005,7 +5000,7 @@
       <c r="F186"/>
       <c r="G186"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187"/>
       <c r="B187"/>
       <c r="C187"/>
@@ -5014,7 +5009,7 @@
       <c r="F187"/>
       <c r="G187"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188"/>
       <c r="B188"/>
       <c r="C188"/>
@@ -5023,7 +5018,7 @@
       <c r="F188"/>
       <c r="G188"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189"/>
       <c r="B189"/>
       <c r="C189"/>
@@ -5032,7 +5027,7 @@
       <c r="F189"/>
       <c r="G189"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190"/>
       <c r="B190"/>
       <c r="C190"/>
@@ -5041,7 +5036,7 @@
       <c r="F190"/>
       <c r="G190"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191"/>
       <c r="B191"/>
       <c r="C191"/>
@@ -5050,7 +5045,7 @@
       <c r="F191"/>
       <c r="G191"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192"/>
       <c r="B192"/>
       <c r="C192"/>
@@ -5059,7 +5054,7 @@
       <c r="F192"/>
       <c r="G192"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193"/>
       <c r="B193"/>
       <c r="C193"/>
@@ -5068,7 +5063,7 @@
       <c r="F193"/>
       <c r="G193"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194"/>
       <c r="B194"/>
       <c r="C194"/>
@@ -5077,7 +5072,7 @@
       <c r="F194"/>
       <c r="G194"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195"/>
       <c r="B195"/>
       <c r="C195"/>
@@ -5086,7 +5081,7 @@
       <c r="F195"/>
       <c r="G195"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196"/>
       <c r="B196"/>
       <c r="C196"/>
@@ -5095,7 +5090,7 @@
       <c r="F196"/>
       <c r="G196"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197"/>
       <c r="B197"/>
       <c r="C197"/>
@@ -5104,7 +5099,7 @@
       <c r="F197"/>
       <c r="G197"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198"/>
       <c r="B198"/>
       <c r="C198"/>
@@ -5113,7 +5108,7 @@
       <c r="F198"/>
       <c r="G198"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199"/>
       <c r="B199"/>
       <c r="C199"/>
@@ -5122,7 +5117,7 @@
       <c r="F199"/>
       <c r="G199"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200"/>
       <c r="B200"/>
       <c r="C200"/>
@@ -5131,7 +5126,7 @@
       <c r="F200"/>
       <c r="G200"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201"/>
       <c r="B201"/>
       <c r="C201"/>
@@ -5140,7 +5135,7 @@
       <c r="F201"/>
       <c r="G201"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202"/>
       <c r="B202"/>
       <c r="C202"/>
@@ -5149,7 +5144,7 @@
       <c r="F202"/>
       <c r="G202"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203"/>
       <c r="B203"/>
       <c r="C203"/>
@@ -5158,7 +5153,7 @@
       <c r="F203"/>
       <c r="G203"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204"/>
       <c r="B204"/>
       <c r="C204"/>
@@ -5167,7 +5162,7 @@
       <c r="F204"/>
       <c r="G204"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205"/>
       <c r="B205"/>
       <c r="C205"/>
@@ -5176,7 +5171,7 @@
       <c r="F205"/>
       <c r="G205"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206"/>
       <c r="B206"/>
       <c r="C206"/>
@@ -5185,7 +5180,7 @@
       <c r="F206"/>
       <c r="G206"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207"/>
       <c r="B207"/>
       <c r="C207"/>
@@ -5194,7 +5189,7 @@
       <c r="F207"/>
       <c r="G207"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208"/>
       <c r="B208"/>
       <c r="C208"/>
@@ -5203,7 +5198,7 @@
       <c r="F208"/>
       <c r="G208"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209"/>
       <c r="B209"/>
       <c r="C209"/>
@@ -5212,7 +5207,7 @@
       <c r="F209"/>
       <c r="G209"/>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210"/>
       <c r="B210"/>
       <c r="C210"/>
@@ -5221,7 +5216,7 @@
       <c r="F210"/>
       <c r="G210"/>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211"/>
       <c r="B211"/>
       <c r="C211"/>
@@ -5230,7 +5225,7 @@
       <c r="F211"/>
       <c r="G211"/>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212"/>
       <c r="B212"/>
       <c r="C212"/>
@@ -5239,7 +5234,7 @@
       <c r="F212"/>
       <c r="G212"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213"/>
       <c r="B213"/>
       <c r="C213"/>
@@ -5248,7 +5243,7 @@
       <c r="F213"/>
       <c r="G213"/>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214"/>
       <c r="B214"/>
       <c r="C214"/>
@@ -5257,7 +5252,7 @@
       <c r="F214"/>
       <c r="G214"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215"/>
       <c r="B215"/>
       <c r="C215"/>
@@ -5266,7 +5261,7 @@
       <c r="F215"/>
       <c r="G215"/>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216"/>
       <c r="B216"/>
       <c r="C216"/>
@@ -5275,7 +5270,7 @@
       <c r="F216"/>
       <c r="G216"/>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217"/>
       <c r="B217"/>
       <c r="C217"/>
@@ -5284,7 +5279,7 @@
       <c r="F217"/>
       <c r="G217"/>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218"/>
       <c r="B218"/>
       <c r="C218"/>
@@ -5293,7 +5288,7 @@
       <c r="F218"/>
       <c r="G218"/>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219"/>
       <c r="B219"/>
       <c r="C219"/>
@@ -5302,7 +5297,7 @@
       <c r="F219"/>
       <c r="G219"/>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220"/>
       <c r="B220"/>
       <c r="C220"/>
@@ -5311,7 +5306,7 @@
       <c r="F220"/>
       <c r="G220"/>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221"/>
       <c r="B221"/>
       <c r="C221"/>
@@ -5320,7 +5315,7 @@
       <c r="F221"/>
       <c r="G221"/>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222"/>
       <c r="B222"/>
       <c r="C222"/>
@@ -5329,7 +5324,7 @@
       <c r="F222"/>
       <c r="G222"/>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223"/>
       <c r="B223"/>
       <c r="C223"/>
@@ -5338,7 +5333,7 @@
       <c r="F223"/>
       <c r="G223"/>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224"/>
       <c r="B224"/>
       <c r="C224"/>
@@ -5347,7 +5342,7 @@
       <c r="F224"/>
       <c r="G224"/>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225"/>
       <c r="B225"/>
       <c r="C225"/>
@@ -5356,7 +5351,7 @@
       <c r="F225"/>
       <c r="G225"/>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226"/>
       <c r="B226"/>
       <c r="C226"/>
@@ -5365,7 +5360,7 @@
       <c r="F226"/>
       <c r="G226"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227"/>
       <c r="B227"/>
       <c r="C227"/>
@@ -5374,7 +5369,7 @@
       <c r="F227"/>
       <c r="G227"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228"/>
       <c r="B228"/>
       <c r="C228"/>
@@ -5383,7 +5378,7 @@
       <c r="F228"/>
       <c r="G228"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229"/>
       <c r="B229"/>
       <c r="C229"/>
@@ -5392,7 +5387,7 @@
       <c r="F229"/>
       <c r="G229"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230"/>
       <c r="B230"/>
       <c r="C230"/>
@@ -5401,7 +5396,7 @@
       <c r="F230"/>
       <c r="G230"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231"/>
       <c r="B231"/>
       <c r="C231"/>
@@ -5410,7 +5405,7 @@
       <c r="F231"/>
       <c r="G231"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232"/>
       <c r="B232"/>
       <c r="C232"/>
@@ -5419,7 +5414,7 @@
       <c r="F232"/>
       <c r="G232"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233"/>
       <c r="B233"/>
       <c r="C233"/>
@@ -5428,7 +5423,7 @@
       <c r="F233"/>
       <c r="G233"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234"/>
       <c r="B234"/>
       <c r="C234"/>
@@ -5437,7 +5432,7 @@
       <c r="F234"/>
       <c r="G234"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235"/>
       <c r="B235"/>
       <c r="C235"/>
@@ -5446,7 +5441,7 @@
       <c r="F235"/>
       <c r="G235"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236"/>
       <c r="B236"/>
       <c r="C236"/>
@@ -5455,7 +5450,7 @@
       <c r="F236"/>
       <c r="G236"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237"/>
       <c r="B237"/>
       <c r="C237"/>
@@ -5464,7 +5459,7 @@
       <c r="F237"/>
       <c r="G237"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238"/>
       <c r="B238"/>
       <c r="C238"/>
@@ -5473,7 +5468,7 @@
       <c r="F238"/>
       <c r="G238"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239"/>
       <c r="B239"/>
       <c r="C239"/>
@@ -5482,7 +5477,7 @@
       <c r="F239"/>
       <c r="G239"/>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240"/>
       <c r="B240"/>
       <c r="C240"/>
@@ -5491,7 +5486,7 @@
       <c r="F240"/>
       <c r="G240"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241"/>
       <c r="B241"/>
       <c r="C241"/>
@@ -5500,7 +5495,7 @@
       <c r="F241"/>
       <c r="G241"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242"/>
       <c r="B242"/>
       <c r="C242"/>
@@ -5509,7 +5504,7 @@
       <c r="F242"/>
       <c r="G242"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243"/>
       <c r="B243"/>
       <c r="C243"/>
@@ -5518,7 +5513,7 @@
       <c r="F243"/>
       <c r="G243"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244"/>
       <c r="B244"/>
       <c r="C244"/>
@@ -5527,7 +5522,7 @@
       <c r="F244"/>
       <c r="G244"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245"/>
       <c r="B245"/>
       <c r="C245"/>
@@ -5536,7 +5531,7 @@
       <c r="F245"/>
       <c r="G245"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246"/>
       <c r="B246"/>
       <c r="C246"/>
@@ -5545,7 +5540,7 @@
       <c r="F246"/>
       <c r="G246"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247"/>
       <c r="B247"/>
       <c r="C247"/>
@@ -5554,7 +5549,7 @@
       <c r="F247"/>
       <c r="G247"/>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248"/>
       <c r="B248"/>
       <c r="C248"/>
@@ -5563,7 +5558,7 @@
       <c r="F248"/>
       <c r="G248"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249"/>
       <c r="B249"/>
       <c r="C249"/>
@@ -5572,7 +5567,7 @@
       <c r="F249"/>
       <c r="G249"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250"/>
       <c r="B250"/>
       <c r="C250"/>
@@ -5581,7 +5576,7 @@
       <c r="F250"/>
       <c r="G250"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251"/>
       <c r="B251"/>
       <c r="C251"/>
@@ -5590,7 +5585,7 @@
       <c r="F251"/>
       <c r="G251"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252"/>
       <c r="B252"/>
       <c r="C252"/>
@@ -5599,7 +5594,7 @@
       <c r="F252"/>
       <c r="G252"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253"/>
       <c r="B253"/>
       <c r="C253"/>
@@ -5608,7 +5603,7 @@
       <c r="F253"/>
       <c r="G253"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254"/>
       <c r="B254"/>
       <c r="C254"/>
@@ -5617,7 +5612,7 @@
       <c r="F254"/>
       <c r="G254"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255"/>
       <c r="B255"/>
       <c r="C255"/>
@@ -5626,7 +5621,7 @@
       <c r="F255"/>
       <c r="G255"/>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256"/>
       <c r="B256"/>
       <c r="C256"/>
@@ -5635,7 +5630,7 @@
       <c r="F256"/>
       <c r="G256"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257"/>
       <c r="B257"/>
       <c r="C257"/>
@@ -5644,7 +5639,7 @@
       <c r="F257"/>
       <c r="G257"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258"/>
       <c r="B258"/>
       <c r="C258"/>
@@ -5653,7 +5648,7 @@
       <c r="F258"/>
       <c r="G258"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259"/>
       <c r="B259"/>
       <c r="C259"/>
@@ -5662,7 +5657,7 @@
       <c r="F259"/>
       <c r="G259"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260"/>
       <c r="B260"/>
       <c r="C260"/>
@@ -5671,7 +5666,7 @@
       <c r="F260"/>
       <c r="G260"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261"/>
       <c r="B261"/>
       <c r="C261"/>
@@ -5680,7 +5675,7 @@
       <c r="F261"/>
       <c r="G261"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262"/>
       <c r="B262"/>
       <c r="C262"/>
@@ -5689,7 +5684,7 @@
       <c r="F262"/>
       <c r="G262"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263"/>
       <c r="B263"/>
       <c r="C263"/>
@@ -5698,7 +5693,7 @@
       <c r="F263"/>
       <c r="G263"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264"/>
       <c r="B264"/>
       <c r="C264"/>
@@ -5707,7 +5702,7 @@
       <c r="F264"/>
       <c r="G264"/>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265"/>
       <c r="B265"/>
       <c r="C265"/>
@@ -5716,7 +5711,7 @@
       <c r="F265"/>
       <c r="G265"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266"/>
       <c r="B266"/>
       <c r="C266"/>
@@ -5725,7 +5720,7 @@
       <c r="F266"/>
       <c r="G266"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267"/>
       <c r="B267"/>
       <c r="C267"/>
@@ -5734,7 +5729,7 @@
       <c r="F267"/>
       <c r="G267"/>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268"/>
       <c r="B268"/>
       <c r="C268"/>
@@ -5743,7 +5738,7 @@
       <c r="F268"/>
       <c r="G268"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269"/>
       <c r="B269"/>
       <c r="C269"/>
@@ -5752,7 +5747,7 @@
       <c r="F269"/>
       <c r="G269"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270"/>
       <c r="B270"/>
       <c r="C270"/>
@@ -5761,7 +5756,7 @@
       <c r="F270"/>
       <c r="G270"/>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271"/>
       <c r="B271"/>
       <c r="C271"/>
@@ -5770,7 +5765,7 @@
       <c r="F271"/>
       <c r="G271"/>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272"/>
       <c r="B272"/>
       <c r="C272"/>
@@ -5779,7 +5774,7 @@
       <c r="F272"/>
       <c r="G272"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273"/>
       <c r="B273"/>
       <c r="C273"/>
@@ -5788,7 +5783,7 @@
       <c r="F273"/>
       <c r="G273"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274"/>
       <c r="B274"/>
       <c r="C274"/>
@@ -5797,7 +5792,7 @@
       <c r="F274"/>
       <c r="G274"/>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275"/>
       <c r="B275"/>
       <c r="C275"/>
@@ -5806,7 +5801,7 @@
       <c r="F275"/>
       <c r="G275"/>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276"/>
       <c r="B276"/>
       <c r="C276"/>
@@ -5815,7 +5810,7 @@
       <c r="F276"/>
       <c r="G276"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277"/>
       <c r="B277"/>
       <c r="C277"/>
@@ -5824,7 +5819,7 @@
       <c r="F277"/>
       <c r="G277"/>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278"/>
       <c r="B278"/>
       <c r="C278"/>
@@ -5833,7 +5828,7 @@
       <c r="F278"/>
       <c r="G278"/>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279"/>
       <c r="B279"/>
       <c r="C279"/>
@@ -5842,7 +5837,7 @@
       <c r="F279"/>
       <c r="G279"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280"/>
       <c r="B280"/>
       <c r="C280"/>
@@ -5851,7 +5846,7 @@
       <c r="F280"/>
       <c r="G280"/>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281"/>
       <c r="B281"/>
       <c r="C281"/>
@@ -5860,7 +5855,7 @@
       <c r="F281"/>
       <c r="G281"/>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282"/>
       <c r="B282"/>
       <c r="C282"/>
@@ -5869,7 +5864,7 @@
       <c r="F282"/>
       <c r="G282"/>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283"/>
       <c r="B283"/>
       <c r="C283"/>
@@ -5878,7 +5873,7 @@
       <c r="F283"/>
       <c r="G283"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284"/>
       <c r="B284"/>
       <c r="C284"/>
@@ -5887,7 +5882,7 @@
       <c r="F284"/>
       <c r="G284"/>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285"/>
       <c r="B285"/>
       <c r="C285"/>
@@ -5896,7 +5891,7 @@
       <c r="F285"/>
       <c r="G285"/>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286"/>
       <c r="B286"/>
       <c r="C286"/>
@@ -5905,7 +5900,7 @@
       <c r="F286"/>
       <c r="G286"/>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287"/>
       <c r="B287"/>
       <c r="C287"/>
@@ -5914,7 +5909,7 @@
       <c r="F287"/>
       <c r="G287"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288"/>
       <c r="B288"/>
       <c r="C288"/>
@@ -5923,7 +5918,7 @@
       <c r="F288"/>
       <c r="G288"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289"/>
       <c r="B289"/>
       <c r="C289"/>
@@ -5932,7 +5927,7 @@
       <c r="F289"/>
       <c r="G289"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290"/>
       <c r="B290"/>
       <c r="C290"/>
@@ -5941,7 +5936,7 @@
       <c r="F290"/>
       <c r="G290"/>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291"/>
       <c r="B291"/>
       <c r="C291"/>
@@ -5950,7 +5945,7 @@
       <c r="F291"/>
       <c r="G291"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292"/>
       <c r="B292"/>
       <c r="C292"/>
@@ -5959,7 +5954,7 @@
       <c r="F292"/>
       <c r="G292"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293"/>
       <c r="B293"/>
       <c r="C293"/>
@@ -5968,7 +5963,7 @@
       <c r="F293"/>
       <c r="G293"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294"/>
       <c r="B294"/>
       <c r="C294"/>
@@ -5977,7 +5972,7 @@
       <c r="F294"/>
       <c r="G294"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295"/>
       <c r="B295"/>
       <c r="C295"/>
@@ -5986,7 +5981,7 @@
       <c r="F295"/>
       <c r="G295"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296"/>
       <c r="B296"/>
       <c r="C296"/>
@@ -5995,7 +5990,7 @@
       <c r="F296"/>
       <c r="G296"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297"/>
       <c r="B297"/>
       <c r="C297"/>
@@ -6004,7 +5999,7 @@
       <c r="F297"/>
       <c r="G297"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298"/>
       <c r="B298"/>
       <c r="C298"/>
@@ -6013,7 +6008,7 @@
       <c r="F298"/>
       <c r="G298"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299"/>
       <c r="B299"/>
       <c r="C299"/>
@@ -6022,7 +6017,7 @@
       <c r="F299"/>
       <c r="G299"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300"/>
       <c r="B300"/>
       <c r="C300"/>
@@ -6031,7 +6026,7 @@
       <c r="F300"/>
       <c r="G300"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301"/>
       <c r="B301"/>
       <c r="C301"/>
@@ -6040,7 +6035,7 @@
       <c r="F301"/>
       <c r="G301"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302"/>
       <c r="B302"/>
       <c r="C302"/>
@@ -6049,7 +6044,7 @@
       <c r="F302"/>
       <c r="G302"/>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303"/>
       <c r="B303"/>
       <c r="C303"/>
@@ -6058,7 +6053,7 @@
       <c r="F303"/>
       <c r="G303"/>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304"/>
       <c r="B304"/>
       <c r="C304"/>
@@ -6067,7 +6062,7 @@
       <c r="F304"/>
       <c r="G304"/>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A305"/>
       <c r="B305"/>
       <c r="C305"/>
@@ -6076,7 +6071,7 @@
       <c r="F305"/>
       <c r="G305"/>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A306"/>
       <c r="B306"/>
       <c r="C306"/>
@@ -6085,7 +6080,7 @@
       <c r="F306"/>
       <c r="G306"/>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A307"/>
       <c r="B307"/>
       <c r="C307"/>
@@ -6094,7 +6089,7 @@
       <c r="F307"/>
       <c r="G307"/>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A308"/>
       <c r="B308"/>
       <c r="C308"/>
@@ -6103,7 +6098,7 @@
       <c r="F308"/>
       <c r="G308"/>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A309"/>
       <c r="B309"/>
       <c r="C309"/>
@@ -6112,7 +6107,7 @@
       <c r="F309"/>
       <c r="G309"/>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A310"/>
       <c r="B310"/>
       <c r="C310"/>
@@ -6121,7 +6116,7 @@
       <c r="F310"/>
       <c r="G310"/>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A311"/>
       <c r="B311"/>
       <c r="C311"/>
@@ -6130,7 +6125,7 @@
       <c r="F311"/>
       <c r="G311"/>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A312"/>
       <c r="B312"/>
       <c r="C312"/>
@@ -6139,7 +6134,7 @@
       <c r="F312"/>
       <c r="G312"/>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A313"/>
       <c r="B313"/>
       <c r="C313"/>
@@ -6148,7 +6143,7 @@
       <c r="F313"/>
       <c r="G313"/>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A314"/>
       <c r="B314"/>
       <c r="C314"/>
@@ -6157,7 +6152,7 @@
       <c r="F314"/>
       <c r="G314"/>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A315"/>
       <c r="B315"/>
       <c r="C315"/>
@@ -6166,7 +6161,7 @@
       <c r="F315"/>
       <c r="G315"/>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A316"/>
       <c r="B316"/>
       <c r="C316"/>
@@ -6175,7 +6170,7 @@
       <c r="F316"/>
       <c r="G316"/>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A317"/>
       <c r="B317"/>
       <c r="C317"/>
@@ -6184,7 +6179,7 @@
       <c r="F317"/>
       <c r="G317"/>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A318"/>
       <c r="B318"/>
       <c r="C318"/>
@@ -6193,7 +6188,7 @@
       <c r="F318"/>
       <c r="G318"/>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A319"/>
       <c r="B319"/>
       <c r="C319"/>
@@ -6202,7 +6197,7 @@
       <c r="F319"/>
       <c r="G319"/>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A320"/>
       <c r="B320"/>
       <c r="C320"/>
@@ -6211,7 +6206,7 @@
       <c r="F320"/>
       <c r="G320"/>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A321"/>
       <c r="B321"/>
       <c r="C321"/>
@@ -6220,7 +6215,7 @@
       <c r="F321"/>
       <c r="G321"/>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A322"/>
       <c r="B322"/>
       <c r="C322"/>
@@ -6229,7 +6224,7 @@
       <c r="F322"/>
       <c r="G322"/>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A323"/>
       <c r="B323"/>
       <c r="C323"/>
@@ -6238,7 +6233,7 @@
       <c r="F323"/>
       <c r="G323"/>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A324"/>
       <c r="B324"/>
       <c r="C324"/>
@@ -6247,7 +6242,7 @@
       <c r="F324"/>
       <c r="G324"/>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A325"/>
       <c r="B325"/>
       <c r="C325"/>
@@ -6256,7 +6251,7 @@
       <c r="F325"/>
       <c r="G325"/>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A326"/>
       <c r="B326"/>
       <c r="C326"/>
@@ -6265,7 +6260,7 @@
       <c r="F326"/>
       <c r="G326"/>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327"/>
       <c r="B327"/>
       <c r="C327"/>
@@ -6274,7 +6269,7 @@
       <c r="F327"/>
       <c r="G327"/>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A328"/>
       <c r="B328"/>
       <c r="C328"/>
@@ -6283,7 +6278,7 @@
       <c r="F328"/>
       <c r="G328"/>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A329"/>
       <c r="B329"/>
       <c r="C329"/>
@@ -6292,7 +6287,7 @@
       <c r="F329"/>
       <c r="G329"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A330"/>
       <c r="B330"/>
       <c r="C330"/>
@@ -6301,7 +6296,7 @@
       <c r="F330"/>
       <c r="G330"/>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A331"/>
       <c r="B331"/>
       <c r="C331"/>
@@ -6310,7 +6305,7 @@
       <c r="F331"/>
       <c r="G331"/>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A332"/>
       <c r="B332"/>
       <c r="C332"/>
@@ -6319,7 +6314,7 @@
       <c r="F332"/>
       <c r="G332"/>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A333"/>
       <c r="B333"/>
       <c r="C333"/>
@@ -6328,7 +6323,7 @@
       <c r="F333"/>
       <c r="G333"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A334"/>
       <c r="B334"/>
       <c r="C334"/>
@@ -6337,7 +6332,7 @@
       <c r="F334"/>
       <c r="G334"/>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A335"/>
       <c r="B335"/>
       <c r="C335"/>
@@ -6346,7 +6341,7 @@
       <c r="F335"/>
       <c r="G335"/>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A336"/>
       <c r="B336"/>
       <c r="C336"/>
@@ -6355,7 +6350,7 @@
       <c r="F336"/>
       <c r="G336"/>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A337"/>
       <c r="B337"/>
       <c r="C337"/>
@@ -6364,7 +6359,7 @@
       <c r="F337"/>
       <c r="G337"/>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A338"/>
       <c r="B338"/>
       <c r="C338"/>
@@ -6373,7 +6368,7 @@
       <c r="F338"/>
       <c r="G338"/>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339"/>
       <c r="B339"/>
       <c r="C339"/>
@@ -6382,7 +6377,7 @@
       <c r="F339"/>
       <c r="G339"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A340"/>
       <c r="B340"/>
       <c r="C340"/>
@@ -6391,7 +6386,7 @@
       <c r="F340"/>
       <c r="G340"/>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A341"/>
       <c r="B341"/>
       <c r="C341"/>
@@ -6400,7 +6395,7 @@
       <c r="F341"/>
       <c r="G341"/>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A342"/>
       <c r="B342"/>
       <c r="C342"/>
@@ -6409,7 +6404,7 @@
       <c r="F342"/>
       <c r="G342"/>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A343"/>
       <c r="B343"/>
       <c r="C343"/>
@@ -6430,38 +6425,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C70400-604D-4BDB-8B2E-DB329A2DDA75}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="F1" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="37"/>
@@ -6470,7 +6465,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="37"/>
@@ -6479,7 +6474,7 @@
       <c r="F3" s="33"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="37"/>
@@ -6488,7 +6483,7 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="37"/>
@@ -6497,7 +6492,7 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="37"/>
@@ -6506,7 +6501,7 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="37"/>
@@ -6515,7 +6510,7 @@
       <c r="F7" s="33"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="37"/>
@@ -6524,7 +6519,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="37"/>
@@ -6533,7 +6528,7 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="37"/>
@@ -6542,7 +6537,7 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="37"/>
@@ -6551,7 +6546,7 @@
       <c r="F11" s="33"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="37"/>
@@ -6560,7 +6555,7 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="37"/>
@@ -6569,7 +6564,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="37"/>
@@ -6578,7 +6573,7 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="37"/>
@@ -6587,7 +6582,7 @@
       <c r="F15" s="33"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="37"/>
@@ -6596,7 +6591,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="37"/>
@@ -6605,7 +6600,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="37"/>
@@ -6614,7 +6609,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="37"/>
@@ -6623,7 +6618,7 @@
       <c r="F19" s="33"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="37"/>
@@ -6632,7 +6627,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="37"/>
@@ -6641,7 +6636,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="37"/>
@@ -6650,7 +6645,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="37"/>
@@ -6659,7 +6654,7 @@
       <c r="F23" s="33"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="37"/>
@@ -6668,7 +6663,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="37"/>
@@ -6685,39 +6680,39 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B98AEC75-CD50-480C-BDD1-969BDB4F802E}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="F1" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H1" s="45" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H1" s="44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="37"/>
@@ -6725,13 +6720,13 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="46" t="str">
+      <c r="H2" s="45" t="str">
         <f>IF(F2="N",A2,A2&amp;CHAR(10)&amp;F2)</f>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="37"/>
@@ -6739,13 +6734,13 @@
       <c r="E3" s="1"/>
       <c r="F3" s="33"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="46" t="str">
+      <c r="H3" s="45" t="str">
         <f>IF(F3="N",A3,A3&amp;CHAR(10)&amp;F3)</f>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="37"/>
@@ -6753,13 +6748,13 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="46" t="str">
+      <c r="H4" s="45" t="str">
         <f t="shared" ref="H4:H31" si="0">IF(F4="N",A4,A4&amp;CHAR(10)&amp;F4)</f>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="37"/>
@@ -6767,13 +6762,13 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="46" t="str">
+      <c r="H5" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="37"/>
@@ -6781,13 +6776,13 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="46" t="str">
+      <c r="H6" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="37"/>
@@ -6795,13 +6790,13 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="46" t="str">
+      <c r="H7" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="37"/>
@@ -6809,13 +6804,13 @@
       <c r="E8" s="1"/>
       <c r="F8" s="33"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="46" t="str">
+      <c r="H8" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="37"/>
@@ -6823,13 +6818,13 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="46" t="str">
+      <c r="H9" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="37"/>
@@ -6837,13 +6832,13 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="46" t="str">
+      <c r="H10" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="37"/>
@@ -6851,13 +6846,13 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="46" t="str">
+      <c r="H11" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="37"/>
@@ -6865,13 +6860,13 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="46" t="str">
+      <c r="H12" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="37"/>
@@ -6879,13 +6874,13 @@
       <c r="E13" s="1"/>
       <c r="F13" s="33"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="46" t="str">
+      <c r="H13" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="37"/>
@@ -6893,13 +6888,13 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="46" t="str">
+      <c r="H14" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="37"/>
@@ -6907,13 +6902,13 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="46" t="str">
+      <c r="H15" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="37"/>
@@ -6921,13 +6916,13 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="46" t="str">
+      <c r="H16" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="37"/>
@@ -6935,13 +6930,13 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="H17" s="46" t="str">
+      <c r="H17" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="37"/>
@@ -6949,13 +6944,13 @@
       <c r="E18" s="1"/>
       <c r="F18" s="33"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="46" t="str">
+      <c r="H18" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="37"/>
@@ -6963,13 +6958,13 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="46" t="str">
+      <c r="H19" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="37"/>
@@ -6977,13 +6972,13 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="46" t="str">
+      <c r="H20" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="37"/>
@@ -6991,13 +6986,13 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="46" t="str">
+      <c r="H21" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="37"/>
@@ -7005,13 +7000,13 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="46" t="str">
+      <c r="H22" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="37"/>
@@ -7019,13 +7014,13 @@
       <c r="E23" s="1"/>
       <c r="F23" s="33"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="46" t="str">
+      <c r="H23" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="37"/>
@@ -7033,13 +7028,13 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="H24" s="46" t="str">
+      <c r="H24" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="37"/>
@@ -7047,13 +7042,13 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="46" t="str">
+      <c r="H25" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="37"/>
@@ -7061,13 +7056,13 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="46" t="str">
+      <c r="H26" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="37"/>
@@ -7075,13 +7070,13 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="46" t="str">
+      <c r="H27" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="37"/>
@@ -7089,13 +7084,13 @@
       <c r="E28" s="1"/>
       <c r="F28" s="33"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="46" t="str">
+      <c r="H28" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="37"/>
@@ -7103,13 +7098,13 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="46" t="str">
+      <c r="H29" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="37"/>
@@ -7117,13 +7112,13 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="46" t="str">
+      <c r="H30" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="37"/>
@@ -7131,7 +7126,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="46" t="str">
+      <c r="H31" s="45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">
 </v>
@@ -7143,6 +7138,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100678F2DA36292A241BB6B602A04ACAAD9" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0e65193b06eae86f79c3903a4a9f0dcf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="167cb1e9-24b5-43e0-9f5d-14a54474cc90" xmlns:ns3="fbf6f0f6-9634-473c-8838-2f74fc79f714" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="03593a2a675d04ffa4dc626c9c15704c" ns2:_="" ns3:_="">
     <xsd:import namespace="167cb1e9-24b5-43e0-9f5d-14a54474cc90"/>
@@ -7397,15 +7401,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7418,6 +7413,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9A0347-3472-4A1D-8404-53EC21279416}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0474098-CD96-40F4-8A28-4082780E5EB1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7436,14 +7439,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9A0347-3472-4A1D-8404-53EC21279416}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6928EB07-F497-4032-8701-AD7E4A30F74A}">
   <ds:schemaRefs>
